--- a/LoteriasExcel/Milionária_edt.xlsx
+++ b/LoteriasExcel/Milionária_edt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADCF8AF-73E9-4607-8E21-8592F1EE9458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A475F78-E54F-4040-A80B-B039C0D887E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="1365" windowWidth="23610" windowHeight="9420" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="67995" yWindow="5595" windowWidth="18630" windowHeight="9465" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="+ MILIONÁRIA" sheetId="12" r:id="rId1"/>
@@ -112,12 +112,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -11528,32 +11527,61 @@
       </c>
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A383" s="2">
+      <c r="A383">
         <v>382</v>
       </c>
-      <c r="B383" s="3">
+      <c r="B383">
         <v>10</v>
       </c>
-      <c r="C383" s="3">
+      <c r="C383">
         <v>17</v>
       </c>
-      <c r="D383" s="3">
+      <c r="D383">
         <v>23</v>
       </c>
-      <c r="E383" s="3">
+      <c r="E383">
         <v>30</v>
       </c>
-      <c r="F383" s="3">
+      <c r="F383">
         <v>44</v>
       </c>
-      <c r="G383" s="3">
+      <c r="G383">
         <v>48</v>
       </c>
-      <c r="H383" s="3">
-        <v>4</v>
-      </c>
-      <c r="I383" s="3">
-        <v>6</v>
+      <c r="H383">
+        <v>4</v>
+      </c>
+      <c r="I383">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A384">
+        <v>383</v>
+      </c>
+      <c r="B384" s="2">
+        <v>3</v>
+      </c>
+      <c r="C384" s="2">
+        <v>4</v>
+      </c>
+      <c r="D384" s="2">
+        <v>16</v>
+      </c>
+      <c r="E384" s="2">
+        <v>18</v>
+      </c>
+      <c r="F384" s="2">
+        <v>39</v>
+      </c>
+      <c r="G384" s="2">
+        <v>45</v>
+      </c>
+      <c r="H384" s="2">
+        <v>1</v>
+      </c>
+      <c r="I384" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="394" spans="2:2" x14ac:dyDescent="0.45">
@@ -11568,13 +11596,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11746,21 +11773,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11786,9 +11811,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Milionária_edt.xlsx
+++ b/LoteriasExcel/Milionária_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A475F78-E54F-4040-A80B-B039C0D887E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32257786-34DD-4B69-9227-5573A8E7E323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67995" yWindow="5595" windowWidth="18630" windowHeight="9465" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="71835" yWindow="465" windowWidth="14565" windowHeight="13800" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="+ MILIONÁRIA" sheetId="12" r:id="rId1"/>
@@ -112,12 +112,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11559,32 +11558,61 @@
       <c r="A384">
         <v>383</v>
       </c>
-      <c r="B384" s="2">
-        <v>3</v>
-      </c>
-      <c r="C384" s="2">
-        <v>4</v>
-      </c>
-      <c r="D384" s="2">
+      <c r="B384">
+        <v>3</v>
+      </c>
+      <c r="C384">
+        <v>4</v>
+      </c>
+      <c r="D384">
         <v>16</v>
       </c>
-      <c r="E384" s="2">
+      <c r="E384">
         <v>18</v>
       </c>
-      <c r="F384" s="2">
+      <c r="F384">
         <v>39</v>
       </c>
-      <c r="G384" s="2">
+      <c r="G384">
         <v>45</v>
       </c>
-      <c r="H384" s="2">
-        <v>1</v>
-      </c>
-      <c r="I384" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="394" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="H384">
+        <v>1</v>
+      </c>
+      <c r="I384">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A385">
+        <v>384</v>
+      </c>
+      <c r="B385">
+        <v>1</v>
+      </c>
+      <c r="C385">
+        <v>14</v>
+      </c>
+      <c r="D385">
+        <v>19</v>
+      </c>
+      <c r="E385">
+        <v>29</v>
+      </c>
+      <c r="F385">
+        <v>31</v>
+      </c>
+      <c r="G385">
+        <v>46</v>
+      </c>
+      <c r="H385">
+        <v>1</v>
+      </c>
+      <c r="I385">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B394" t="s">
         <v>9</v>
       </c>
@@ -11596,12 +11624,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11773,19 +11802,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11811,12 +11842,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Milionária_edt.xlsx
+++ b/LoteriasExcel/Milionária_edt.xlsx
@@ -11624,13 +11624,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11802,21 +11801,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11842,9 +11839,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Milionária_edt.xlsx
+++ b/LoteriasExcel/Milionária_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32257786-34DD-4B69-9227-5573A8E7E323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F559841-A36E-4705-BB11-FBC10B7CA61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71835" yWindow="465" windowWidth="14565" windowHeight="13800" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="23504" windowHeight="10350" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="+ MILIONÁRIA" sheetId="12" r:id="rId1"/>
@@ -112,11 +112,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11612,6 +11614,122 @@
         <v>6</v>
       </c>
     </row>
+    <row r="386" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A386" s="2">
+        <v>385</v>
+      </c>
+      <c r="B386" s="3">
+        <v>10</v>
+      </c>
+      <c r="C386" s="3">
+        <v>12</v>
+      </c>
+      <c r="D386" s="3">
+        <v>13</v>
+      </c>
+      <c r="E386" s="3">
+        <v>16</v>
+      </c>
+      <c r="F386" s="3">
+        <v>33</v>
+      </c>
+      <c r="G386" s="3">
+        <v>50</v>
+      </c>
+      <c r="H386" s="3">
+        <v>3</v>
+      </c>
+      <c r="I386" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A387" s="2">
+        <v>386</v>
+      </c>
+      <c r="B387" s="3">
+        <v>14</v>
+      </c>
+      <c r="C387" s="3">
+        <v>16</v>
+      </c>
+      <c r="D387" s="3">
+        <v>19</v>
+      </c>
+      <c r="E387" s="3">
+        <v>32</v>
+      </c>
+      <c r="F387" s="3">
+        <v>34</v>
+      </c>
+      <c r="G387" s="3">
+        <v>35</v>
+      </c>
+      <c r="H387" s="3">
+        <v>4</v>
+      </c>
+      <c r="I387" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A388" s="2">
+        <v>387</v>
+      </c>
+      <c r="B388" s="3">
+        <v>14</v>
+      </c>
+      <c r="C388" s="3">
+        <v>26</v>
+      </c>
+      <c r="D388" s="3">
+        <v>27</v>
+      </c>
+      <c r="E388" s="3">
+        <v>28</v>
+      </c>
+      <c r="F388" s="3">
+        <v>43</v>
+      </c>
+      <c r="G388" s="3">
+        <v>46</v>
+      </c>
+      <c r="H388" s="3">
+        <v>2</v>
+      </c>
+      <c r="I388" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A389" s="2">
+        <v>388</v>
+      </c>
+      <c r="B389" s="3">
+        <v>11</v>
+      </c>
+      <c r="C389" s="3">
+        <v>17</v>
+      </c>
+      <c r="D389" s="3">
+        <v>21</v>
+      </c>
+      <c r="E389" s="3">
+        <v>23</v>
+      </c>
+      <c r="F389" s="3">
+        <v>34</v>
+      </c>
+      <c r="G389" s="3">
+        <v>41</v>
+      </c>
+      <c r="H389" s="3">
+        <v>3</v>
+      </c>
+      <c r="I389" s="3">
+        <v>5</v>
+      </c>
+    </row>
     <row r="394" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B394" t="s">
         <v>9</v>
@@ -11624,12 +11742,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11801,19 +11920,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11839,12 +11960,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Milionária_edt.xlsx
+++ b/LoteriasExcel/Milionária_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F559841-A36E-4705-BB11-FBC10B7CA61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB24C1B-52D0-41AD-9ECF-518E32841C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="23504" windowHeight="10350" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="72825" yWindow="1170" windowWidth="13515" windowHeight="10380" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="+ MILIONÁRIA" sheetId="12" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Concurso</t>
   </si>
@@ -61,9 +61,6 @@
   </si>
   <si>
     <t>Trevo1</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -112,13 +109,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11615,124 +11610,264 @@
       </c>
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A386" s="2">
+      <c r="A386">
         <v>385</v>
       </c>
-      <c r="B386" s="3">
+      <c r="B386">
         <v>10</v>
       </c>
-      <c r="C386" s="3">
+      <c r="C386">
         <v>12</v>
       </c>
-      <c r="D386" s="3">
+      <c r="D386">
         <v>13</v>
       </c>
-      <c r="E386" s="3">
+      <c r="E386">
         <v>16</v>
       </c>
-      <c r="F386" s="3">
+      <c r="F386">
         <v>33</v>
       </c>
-      <c r="G386" s="3">
+      <c r="G386">
         <v>50</v>
       </c>
-      <c r="H386" s="3">
-        <v>3</v>
-      </c>
-      <c r="I386" s="3">
+      <c r="H386">
+        <v>3</v>
+      </c>
+      <c r="I386">
         <v>4</v>
       </c>
     </row>
     <row r="387" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A387" s="2">
+      <c r="A387">
         <v>386</v>
       </c>
-      <c r="B387" s="3">
+      <c r="B387">
         <v>14</v>
       </c>
-      <c r="C387" s="3">
+      <c r="C387">
         <v>16</v>
       </c>
-      <c r="D387" s="3">
+      <c r="D387">
         <v>19</v>
       </c>
-      <c r="E387" s="3">
+      <c r="E387">
         <v>32</v>
       </c>
-      <c r="F387" s="3">
+      <c r="F387">
         <v>34</v>
       </c>
-      <c r="G387" s="3">
+      <c r="G387">
         <v>35</v>
       </c>
-      <c r="H387" s="3">
-        <v>4</v>
-      </c>
-      <c r="I387" s="3">
+      <c r="H387">
+        <v>4</v>
+      </c>
+      <c r="I387">
         <v>5</v>
       </c>
     </row>
     <row r="388" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A388" s="2">
+      <c r="A388">
         <v>387</v>
       </c>
-      <c r="B388" s="3">
+      <c r="B388">
         <v>14</v>
       </c>
-      <c r="C388" s="3">
+      <c r="C388">
         <v>26</v>
       </c>
-      <c r="D388" s="3">
+      <c r="D388">
         <v>27</v>
       </c>
-      <c r="E388" s="3">
+      <c r="E388">
         <v>28</v>
       </c>
-      <c r="F388" s="3">
+      <c r="F388">
         <v>43</v>
       </c>
-      <c r="G388" s="3">
+      <c r="G388">
         <v>46</v>
       </c>
-      <c r="H388" s="3">
-        <v>2</v>
-      </c>
-      <c r="I388" s="3">
+      <c r="H388">
+        <v>2</v>
+      </c>
+      <c r="I388">
         <v>6</v>
       </c>
     </row>
     <row r="389" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A389" s="2">
+      <c r="A389">
         <v>388</v>
       </c>
-      <c r="B389" s="3">
+      <c r="B389">
         <v>11</v>
       </c>
-      <c r="C389" s="3">
+      <c r="C389">
         <v>17</v>
       </c>
-      <c r="D389" s="3">
+      <c r="D389">
         <v>21</v>
       </c>
-      <c r="E389" s="3">
+      <c r="E389">
         <v>23</v>
       </c>
-      <c r="F389" s="3">
+      <c r="F389">
         <v>34</v>
       </c>
-      <c r="G389" s="3">
+      <c r="G389">
         <v>41</v>
       </c>
-      <c r="H389" s="3">
-        <v>3</v>
-      </c>
-      <c r="I389" s="3">
-        <v>5</v>
+      <c r="H389">
+        <v>3</v>
+      </c>
+      <c r="I389">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A390">
+        <v>389</v>
+      </c>
+      <c r="B390">
+        <v>2</v>
+      </c>
+      <c r="C390">
+        <v>14</v>
+      </c>
+      <c r="D390">
+        <v>17</v>
+      </c>
+      <c r="E390">
+        <v>21</v>
+      </c>
+      <c r="F390">
+        <v>42</v>
+      </c>
+      <c r="G390">
+        <v>46</v>
+      </c>
+      <c r="H390">
+        <v>4</v>
+      </c>
+      <c r="I390">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A391">
+        <v>390</v>
+      </c>
+      <c r="B391">
+        <v>2</v>
+      </c>
+      <c r="C391">
+        <v>17</v>
+      </c>
+      <c r="D391">
+        <v>28</v>
+      </c>
+      <c r="E391">
+        <v>37</v>
+      </c>
+      <c r="F391">
+        <v>46</v>
+      </c>
+      <c r="G391">
+        <v>49</v>
+      </c>
+      <c r="H391">
+        <v>1</v>
+      </c>
+      <c r="I391">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="392" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A392">
+        <v>391</v>
+      </c>
+      <c r="B392">
+        <v>4</v>
+      </c>
+      <c r="C392">
+        <v>10</v>
+      </c>
+      <c r="D392">
+        <v>27</v>
+      </c>
+      <c r="E392">
+        <v>40</v>
+      </c>
+      <c r="F392">
+        <v>44</v>
+      </c>
+      <c r="G392">
+        <v>47</v>
+      </c>
+      <c r="H392">
+        <v>3</v>
+      </c>
+      <c r="I392">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A393">
+        <v>392</v>
+      </c>
+      <c r="B393">
+        <v>3</v>
+      </c>
+      <c r="C393">
+        <v>5</v>
+      </c>
+      <c r="D393">
+        <v>12</v>
+      </c>
+      <c r="E393">
+        <v>33</v>
+      </c>
+      <c r="F393">
+        <v>38</v>
+      </c>
+      <c r="G393">
+        <v>45</v>
+      </c>
+      <c r="H393">
+        <v>3</v>
+      </c>
+      <c r="I393">
+        <v>6</v>
       </c>
     </row>
     <row r="394" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="B394" t="s">
-        <v>9</v>
+      <c r="A394">
+        <v>393</v>
+      </c>
+      <c r="B394">
+        <v>2</v>
+      </c>
+      <c r="C394">
+        <v>15</v>
+      </c>
+      <c r="D394">
+        <v>17</v>
+      </c>
+      <c r="E394">
+        <v>26</v>
+      </c>
+      <c r="F394">
+        <v>29</v>
+      </c>
+      <c r="G394">
+        <v>32</v>
+      </c>
+      <c r="H394">
+        <v>4</v>
+      </c>
+      <c r="I394">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -11742,13 +11877,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11920,21 +12054,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11960,9 +12092,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Milionária_edt.xlsx
+++ b/LoteriasExcel/Milionária_edt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB24C1B-52D0-41AD-9ECF-518E32841C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2044A0F-A392-4762-82DD-DD6B8DD289C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="72825" yWindow="1170" windowWidth="13515" windowHeight="10380" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="57825" yWindow="75" windowWidth="19845" windowHeight="11865" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="+ MILIONÁRIA" sheetId="12" r:id="rId1"/>
@@ -109,11 +109,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2F70E5-30B2-4963-A61E-AD5ABF761887}">
-  <dimension ref="A1:I394"/>
+  <dimension ref="A1:I395"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.86328125" bestFit="1" customWidth="1"/>
@@ -11870,6 +11872,35 @@
         <v>5</v>
       </c>
     </row>
+    <row r="395" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A395" s="2">
+        <v>394</v>
+      </c>
+      <c r="B395" s="3">
+        <v>9</v>
+      </c>
+      <c r="C395" s="3">
+        <v>10</v>
+      </c>
+      <c r="D395" s="3">
+        <v>14</v>
+      </c>
+      <c r="E395" s="3">
+        <v>21</v>
+      </c>
+      <c r="F395" s="3">
+        <v>23</v>
+      </c>
+      <c r="G395" s="3">
+        <v>32</v>
+      </c>
+      <c r="H395" s="3">
+        <v>4</v>
+      </c>
+      <c r="I395" s="3">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11877,12 +11908,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12054,19 +12086,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12092,12 +12126,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>